--- a/서버정보/20261001_리소스배포_테스트.xlsx
+++ b/서버정보/20261001_리소스배포_테스트.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5C1A83-54CD-4F04-93E7-2882A2F568CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -31947,21 +31947,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -32105,31 +32090,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32145,4 +32121,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/서버정보/20261001_리소스배포_테스트.xlsx
+++ b/서버정보/20261001_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5C1A83-54CD-4F04-93E7-2882A2F568CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA9CA8C-DC2D-449C-B331-00B48DFB1E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4471" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4466" uniqueCount="612">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -29003,7 +29003,7 @@
         <v>CLV</v>
       </c>
       <c r="D41" s="84" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="E41" s="84" t="s">
         <v>24</v>
@@ -29056,7 +29056,7 @@
         <v>CLV</v>
       </c>
       <c r="D42" s="74" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="E42" s="74" t="s">
         <v>24</v>
@@ -29269,9 +29269,7 @@
         <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($F46, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D46" s="74" t="s">
-        <v>286</v>
-      </c>
+      <c r="D46" s="74"/>
       <c r="E46" s="74" t="s">
         <v>24</v>
       </c>
@@ -29317,9 +29315,7 @@
         <f t="array" ref="C47">UPPER(INDEX(_xlfn.TEXTSPLIT($F47, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D47" s="84" t="s">
-        <v>286</v>
-      </c>
+      <c r="D47" s="84"/>
       <c r="E47" s="84" t="s">
         <v>24</v>
       </c>
@@ -29365,9 +29361,7 @@
         <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($F48, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D48" s="74" t="s">
-        <v>286</v>
-      </c>
+      <c r="D48" s="74"/>
       <c r="E48" s="74" t="s">
         <v>24</v>
       </c>
@@ -29413,9 +29407,7 @@
         <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($F49, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D49" s="84" t="s">
-        <v>286</v>
-      </c>
+      <c r="D49" s="84"/>
       <c r="E49" s="84" t="s">
         <v>24</v>
       </c>
@@ -29461,9 +29453,7 @@
         <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($F50, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D50" s="74" t="s">
-        <v>286</v>
-      </c>
+      <c r="D50" s="74"/>
       <c r="E50" s="74" t="s">
         <v>24</v>
       </c>
@@ -31947,6 +31937,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -32090,22 +32095,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32121,28 +32135,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/서버정보/20261001_리소스배포_테스트.xlsx
+++ b/서버정보/20261001_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA9CA8C-DC2D-449C-B331-00B48DFB1E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FE0391-D697-44F3-840D-4FE34D16B304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29109,7 +29109,7 @@
         <v>CLV</v>
       </c>
       <c r="D43" s="84" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="E43" s="84" t="s">
         <v>24</v>
@@ -29161,8 +29161,8 @@
         <f t="array" ref="C44">UPPER(INDEX(_xlfn.TEXTSPLIT($F44, "-"), 3))</f>
         <v>CLV</v>
       </c>
-      <c r="D44" s="107" t="s">
-        <v>286</v>
+      <c r="D44" s="74" t="s">
+        <v>597</v>
       </c>
       <c r="E44" s="107" t="s">
         <v>24</v>
@@ -29216,7 +29216,7 @@
         <v>CLV</v>
       </c>
       <c r="D45" s="84" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="E45" s="84" t="s">
         <v>24</v>
@@ -31937,21 +31937,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -32095,31 +32080,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32135,4 +32111,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>